--- a/qa-suites/deployment-readiness-report.xlsx
+++ b/qa-suites/deployment-readiness-report.xlsx
@@ -32,7 +32,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>24/7/2026, 6:38:01 pm</t>
+    <t>24/7/2026, 7:24:50 pm</t>
   </si>
   <si>
     <t>Deployment Status</t>
@@ -1778,7 +1778,7 @@
         <v>38</v>
       </c>
       <c r="K2" s="7">
-        <v>411</v>
+        <v>111</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>15</v>
@@ -1816,7 +1816,7 @@
         <v>42</v>
       </c>
       <c r="K3" s="9">
-        <v>113</v>
+        <v>329</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>15</v>
@@ -1854,7 +1854,7 @@
         <v>47</v>
       </c>
       <c r="K4" s="7">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>48</v>
@@ -1892,7 +1892,7 @@
         <v>38</v>
       </c>
       <c r="K5" s="9">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>15</v>
@@ -1930,7 +1930,7 @@
         <v>42</v>
       </c>
       <c r="K6" s="7">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>47</v>
       </c>
       <c r="K7" s="9">
-        <v>269</v>
+        <v>206</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>15</v>
@@ -2006,7 +2006,7 @@
         <v>38</v>
       </c>
       <c r="K8" s="7">
-        <v>453</v>
+        <v>141</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>15</v>
@@ -2044,7 +2044,7 @@
         <v>42</v>
       </c>
       <c r="K9" s="9">
-        <v>331</v>
+        <v>101</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>15</v>
@@ -2082,7 +2082,7 @@
         <v>47</v>
       </c>
       <c r="K10" s="7">
-        <v>113</v>
+        <v>276</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>15</v>
@@ -2120,7 +2120,7 @@
         <v>38</v>
       </c>
       <c r="K11" s="9">
-        <v>414</v>
+        <v>299</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>15</v>
@@ -2158,7 +2158,7 @@
         <v>42</v>
       </c>
       <c r="K12" s="7">
-        <v>457</v>
+        <v>61</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>15</v>
@@ -2196,7 +2196,7 @@
         <v>47</v>
       </c>
       <c r="K13" s="9">
-        <v>412</v>
+        <v>159</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>15</v>
@@ -2234,7 +2234,7 @@
         <v>38</v>
       </c>
       <c r="K14" s="7">
-        <v>93</v>
+        <v>277</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>15</v>
@@ -2272,7 +2272,7 @@
         <v>42</v>
       </c>
       <c r="K15" s="9">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>15</v>
@@ -2310,7 +2310,7 @@
         <v>47</v>
       </c>
       <c r="K16" s="7">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>15</v>
@@ -2348,7 +2348,7 @@
         <v>38</v>
       </c>
       <c r="K17" s="9">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>15</v>
@@ -2386,7 +2386,7 @@
         <v>42</v>
       </c>
       <c r="K18" s="7">
-        <v>400</v>
+        <v>220</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>15</v>
@@ -2424,7 +2424,7 @@
         <v>47</v>
       </c>
       <c r="K19" s="9">
-        <v>112</v>
+        <v>462</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>15</v>
@@ -2462,7 +2462,7 @@
         <v>38</v>
       </c>
       <c r="K20" s="7">
-        <v>241</v>
+        <v>412</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>15</v>
@@ -2500,7 +2500,7 @@
         <v>42</v>
       </c>
       <c r="K21" s="9">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>15</v>
@@ -2538,7 +2538,7 @@
         <v>47</v>
       </c>
       <c r="K22" s="7">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>15</v>
@@ -2576,7 +2576,7 @@
         <v>38</v>
       </c>
       <c r="K23" s="9">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>15</v>
@@ -2614,7 +2614,7 @@
         <v>42</v>
       </c>
       <c r="K24" s="7">
-        <v>469</v>
+        <v>75</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>15</v>
@@ -2652,7 +2652,7 @@
         <v>47</v>
       </c>
       <c r="K25" s="9">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>15</v>
@@ -2690,7 +2690,7 @@
         <v>38</v>
       </c>
       <c r="K26" s="7">
-        <v>392</v>
+        <v>193</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>15</v>
@@ -2728,7 +2728,7 @@
         <v>42</v>
       </c>
       <c r="K27" s="9">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>15</v>
@@ -2766,7 +2766,7 @@
         <v>47</v>
       </c>
       <c r="K28" s="7">
-        <v>338</v>
+        <v>460</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>15</v>
@@ -2804,7 +2804,7 @@
         <v>38</v>
       </c>
       <c r="K29" s="9">
-        <v>157</v>
+        <v>58</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>15</v>
@@ -2842,7 +2842,7 @@
         <v>42</v>
       </c>
       <c r="K30" s="7">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L30" s="11" t="s">
         <v>102</v>
@@ -2880,7 +2880,7 @@
         <v>47</v>
       </c>
       <c r="K31" s="9">
-        <v>203</v>
+        <v>384</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>15</v>
@@ -2918,7 +2918,7 @@
         <v>38</v>
       </c>
       <c r="K32" s="7">
-        <v>40</v>
+        <v>393</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>15</v>
@@ -2994,7 +2994,7 @@
         <v>47</v>
       </c>
       <c r="K34" s="7">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>15</v>
@@ -3032,7 +3032,7 @@
         <v>38</v>
       </c>
       <c r="K35" s="9">
-        <v>443</v>
+        <v>132</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>15</v>
@@ -3070,7 +3070,7 @@
         <v>42</v>
       </c>
       <c r="K36" s="7">
-        <v>426</v>
+        <v>332</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>15</v>
@@ -3108,7 +3108,7 @@
         <v>47</v>
       </c>
       <c r="K37" s="9">
-        <v>419</v>
+        <v>233</v>
       </c>
       <c r="L37" s="8" t="s">
         <v>15</v>
@@ -3146,7 +3146,7 @@
         <v>38</v>
       </c>
       <c r="K38" s="7">
-        <v>284</v>
+        <v>389</v>
       </c>
       <c r="L38" s="8" t="s">
         <v>15</v>
@@ -3184,7 +3184,7 @@
         <v>42</v>
       </c>
       <c r="K39" s="9">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>15</v>
@@ -3222,7 +3222,7 @@
         <v>47</v>
       </c>
       <c r="K40" s="7">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="L40" s="8" t="s">
         <v>15</v>
@@ -3260,7 +3260,7 @@
         <v>38</v>
       </c>
       <c r="K41" s="9">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="L41" s="8" t="s">
         <v>15</v>
@@ -3298,7 +3298,7 @@
         <v>42</v>
       </c>
       <c r="K42" s="7">
-        <v>420</v>
+        <v>208</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>15</v>
@@ -3336,7 +3336,7 @@
         <v>47</v>
       </c>
       <c r="K43" s="9">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>15</v>
@@ -3374,7 +3374,7 @@
         <v>38</v>
       </c>
       <c r="K44" s="7">
-        <v>143</v>
+        <v>442</v>
       </c>
       <c r="L44" s="8" t="s">
         <v>15</v>
@@ -3412,7 +3412,7 @@
         <v>42</v>
       </c>
       <c r="K45" s="9">
-        <v>435</v>
+        <v>140</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>15</v>
@@ -3450,7 +3450,7 @@
         <v>47</v>
       </c>
       <c r="K46" s="7">
-        <v>304</v>
+        <v>68</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>15</v>
@@ -3488,7 +3488,7 @@
         <v>38</v>
       </c>
       <c r="K47" s="9">
-        <v>163</v>
+        <v>361</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>15</v>
@@ -3526,7 +3526,7 @@
         <v>42</v>
       </c>
       <c r="K48" s="7">
-        <v>333</v>
+        <v>68</v>
       </c>
       <c r="L48" s="8" t="s">
         <v>15</v>
@@ -3564,7 +3564,7 @@
         <v>47</v>
       </c>
       <c r="K49" s="9">
-        <v>363</v>
+        <v>460</v>
       </c>
       <c r="L49" s="8" t="s">
         <v>15</v>
@@ -3602,7 +3602,7 @@
         <v>38</v>
       </c>
       <c r="K50" s="7">
-        <v>258</v>
+        <v>412</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>15</v>
@@ -3640,7 +3640,7 @@
         <v>42</v>
       </c>
       <c r="K51" s="9">
-        <v>125</v>
+        <v>261</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>15</v>
@@ -3678,7 +3678,7 @@
         <v>47</v>
       </c>
       <c r="K52" s="7">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>15</v>
@@ -3716,7 +3716,7 @@
         <v>38</v>
       </c>
       <c r="K53" s="9">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>15</v>
@@ -3754,7 +3754,7 @@
         <v>42</v>
       </c>
       <c r="K54" s="7">
-        <v>398</v>
+        <v>441</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>15</v>
@@ -3792,7 +3792,7 @@
         <v>47</v>
       </c>
       <c r="K55" s="9">
-        <v>367</v>
+        <v>140</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>15</v>
@@ -3830,7 +3830,7 @@
         <v>38</v>
       </c>
       <c r="K56" s="7">
-        <v>139</v>
+        <v>262</v>
       </c>
       <c r="L56" s="8" t="s">
         <v>15</v>
@@ -3868,7 +3868,7 @@
         <v>42</v>
       </c>
       <c r="K57" s="9">
-        <v>414</v>
+        <v>306</v>
       </c>
       <c r="L57" s="8" t="s">
         <v>15</v>
@@ -3906,7 +3906,7 @@
         <v>47</v>
       </c>
       <c r="K58" s="7">
-        <v>268</v>
+        <v>455</v>
       </c>
       <c r="L58" s="8" t="s">
         <v>15</v>
@@ -3944,7 +3944,7 @@
         <v>38</v>
       </c>
       <c r="K59" s="9">
-        <v>77</v>
+        <v>376</v>
       </c>
       <c r="L59" s="8" t="s">
         <v>15</v>
@@ -3982,7 +3982,7 @@
         <v>42</v>
       </c>
       <c r="K60" s="7">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>15</v>
@@ -4020,7 +4020,7 @@
         <v>47</v>
       </c>
       <c r="K61" s="9">
-        <v>43</v>
+        <v>397</v>
       </c>
       <c r="L61" s="8" t="s">
         <v>15</v>
@@ -4058,7 +4058,7 @@
         <v>38</v>
       </c>
       <c r="K62" s="7">
-        <v>276</v>
+        <v>392</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>15</v>
@@ -4096,7 +4096,7 @@
         <v>42</v>
       </c>
       <c r="K63" s="9">
-        <v>389</v>
+        <v>435</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>15</v>
@@ -4134,7 +4134,7 @@
         <v>47</v>
       </c>
       <c r="K64" s="7">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="L64" s="8" t="s">
         <v>15</v>
@@ -4172,7 +4172,7 @@
         <v>38</v>
       </c>
       <c r="K65" s="9">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="L65" s="8" t="s">
         <v>15</v>
@@ -4210,7 +4210,7 @@
         <v>42</v>
       </c>
       <c r="K66" s="7">
-        <v>237</v>
+        <v>403</v>
       </c>
       <c r="L66" s="8" t="s">
         <v>15</v>
@@ -4248,7 +4248,7 @@
         <v>47</v>
       </c>
       <c r="K67" s="9">
-        <v>89</v>
+        <v>218</v>
       </c>
       <c r="L67" s="11" t="s">
         <v>102</v>
@@ -4286,7 +4286,7 @@
         <v>38</v>
       </c>
       <c r="K68" s="7">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="L68" s="8" t="s">
         <v>15</v>
@@ -4324,7 +4324,7 @@
         <v>42</v>
       </c>
       <c r="K69" s="9">
-        <v>212</v>
+        <v>295</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>15</v>
@@ -4362,7 +4362,7 @@
         <v>47</v>
       </c>
       <c r="K70" s="7">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>15</v>
@@ -4400,7 +4400,7 @@
         <v>38</v>
       </c>
       <c r="K71" s="9">
-        <v>189</v>
+        <v>288</v>
       </c>
       <c r="L71" s="10" t="s">
         <v>48</v>
@@ -4438,7 +4438,7 @@
         <v>42</v>
       </c>
       <c r="K72" s="7">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="L72" s="8" t="s">
         <v>15</v>
@@ -4476,7 +4476,7 @@
         <v>47</v>
       </c>
       <c r="K73" s="9">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>15</v>
@@ -4514,7 +4514,7 @@
         <v>38</v>
       </c>
       <c r="K74" s="7">
-        <v>324</v>
+        <v>413</v>
       </c>
       <c r="L74" s="8" t="s">
         <v>15</v>
@@ -4552,7 +4552,7 @@
         <v>42</v>
       </c>
       <c r="K75" s="9">
-        <v>216</v>
+        <v>338</v>
       </c>
       <c r="L75" s="8" t="s">
         <v>15</v>
@@ -4590,7 +4590,7 @@
         <v>47</v>
       </c>
       <c r="K76" s="7">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>15</v>
@@ -4628,7 +4628,7 @@
         <v>38</v>
       </c>
       <c r="K77" s="9">
-        <v>131</v>
+        <v>429</v>
       </c>
       <c r="L77" s="8" t="s">
         <v>15</v>
@@ -4666,7 +4666,7 @@
         <v>42</v>
       </c>
       <c r="K78" s="7">
-        <v>376</v>
+        <v>430</v>
       </c>
       <c r="L78" s="8" t="s">
         <v>15</v>
@@ -4704,7 +4704,7 @@
         <v>47</v>
       </c>
       <c r="K79" s="9">
-        <v>59</v>
+        <v>404</v>
       </c>
       <c r="L79" s="8" t="s">
         <v>15</v>
@@ -4742,7 +4742,7 @@
         <v>38</v>
       </c>
       <c r="K80" s="7">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>15</v>
@@ -4780,7 +4780,7 @@
         <v>42</v>
       </c>
       <c r="K81" s="9">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="L81" s="8" t="s">
         <v>15</v>
@@ -4818,7 +4818,7 @@
         <v>47</v>
       </c>
       <c r="K82" s="7">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="L82" s="8" t="s">
         <v>15</v>
@@ -4856,7 +4856,7 @@
         <v>38</v>
       </c>
       <c r="K83" s="9">
-        <v>462</v>
+        <v>61</v>
       </c>
       <c r="L83" s="8" t="s">
         <v>15</v>
@@ -4894,7 +4894,7 @@
         <v>42</v>
       </c>
       <c r="K84" s="7">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="L84" s="8" t="s">
         <v>15</v>
@@ -4932,7 +4932,7 @@
         <v>47</v>
       </c>
       <c r="K85" s="9">
-        <v>291</v>
+        <v>43</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>15</v>
@@ -4970,7 +4970,7 @@
         <v>38</v>
       </c>
       <c r="K86" s="7">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>15</v>
@@ -5008,7 +5008,7 @@
         <v>42</v>
       </c>
       <c r="K87" s="9">
-        <v>344</v>
+        <v>438</v>
       </c>
       <c r="L87" s="8" t="s">
         <v>15</v>
@@ -5046,7 +5046,7 @@
         <v>47</v>
       </c>
       <c r="K88" s="7">
-        <v>231</v>
+        <v>32</v>
       </c>
       <c r="L88" s="8" t="s">
         <v>15</v>
@@ -5084,7 +5084,7 @@
         <v>38</v>
       </c>
       <c r="K89" s="9">
-        <v>44</v>
+        <v>271</v>
       </c>
       <c r="L89" s="8" t="s">
         <v>15</v>
@@ -5122,7 +5122,7 @@
         <v>42</v>
       </c>
       <c r="K90" s="7">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="L90" s="8" t="s">
         <v>15</v>
@@ -5160,7 +5160,7 @@
         <v>47</v>
       </c>
       <c r="K91" s="9">
-        <v>134</v>
+        <v>292</v>
       </c>
       <c r="L91" s="8" t="s">
         <v>15</v>
@@ -5198,7 +5198,7 @@
         <v>38</v>
       </c>
       <c r="K92" s="7">
-        <v>95</v>
+        <v>358</v>
       </c>
       <c r="L92" s="8" t="s">
         <v>15</v>
@@ -5236,7 +5236,7 @@
         <v>42</v>
       </c>
       <c r="K93" s="9">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="L93" s="8" t="s">
         <v>15</v>
@@ -5274,7 +5274,7 @@
         <v>47</v>
       </c>
       <c r="K94" s="7">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="L94" s="8" t="s">
         <v>15</v>
@@ -5312,7 +5312,7 @@
         <v>38</v>
       </c>
       <c r="K95" s="9">
-        <v>224</v>
+        <v>336</v>
       </c>
       <c r="L95" s="8" t="s">
         <v>15</v>
@@ -5350,7 +5350,7 @@
         <v>42</v>
       </c>
       <c r="K96" s="7">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="L96" s="8" t="s">
         <v>15</v>
@@ -5388,7 +5388,7 @@
         <v>47</v>
       </c>
       <c r="K97" s="9">
-        <v>445</v>
+        <v>366</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>15</v>
@@ -5426,7 +5426,7 @@
         <v>38</v>
       </c>
       <c r="K98" s="7">
-        <v>270</v>
+        <v>333</v>
       </c>
       <c r="L98" s="8" t="s">
         <v>15</v>
@@ -5464,7 +5464,7 @@
         <v>42</v>
       </c>
       <c r="K99" s="9">
-        <v>337</v>
+        <v>23</v>
       </c>
       <c r="L99" s="8" t="s">
         <v>15</v>
@@ -5502,7 +5502,7 @@
         <v>47</v>
       </c>
       <c r="K100" s="7">
-        <v>463</v>
+        <v>150</v>
       </c>
       <c r="L100" s="8" t="s">
         <v>15</v>
@@ -5540,7 +5540,7 @@
         <v>38</v>
       </c>
       <c r="K101" s="9">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="L101" s="8" t="s">
         <v>15</v>
@@ -5578,7 +5578,7 @@
         <v>42</v>
       </c>
       <c r="K102" s="7">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="L102" s="8" t="s">
         <v>15</v>
@@ -5616,7 +5616,7 @@
         <v>47</v>
       </c>
       <c r="K103" s="9">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="L103" s="8" t="s">
         <v>15</v>
@@ -5654,7 +5654,7 @@
         <v>38</v>
       </c>
       <c r="K104" s="7">
-        <v>430</v>
+        <v>141</v>
       </c>
       <c r="L104" s="11" t="s">
         <v>102</v>
@@ -5692,7 +5692,7 @@
         <v>42</v>
       </c>
       <c r="K105" s="9">
-        <v>229</v>
+        <v>428</v>
       </c>
       <c r="L105" s="8" t="s">
         <v>15</v>
@@ -5730,7 +5730,7 @@
         <v>47</v>
       </c>
       <c r="K106" s="7">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="L106" s="8" t="s">
         <v>15</v>
@@ -5768,7 +5768,7 @@
         <v>38</v>
       </c>
       <c r="K107" s="9">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="L107" s="8" t="s">
         <v>15</v>
@@ -5806,7 +5806,7 @@
         <v>42</v>
       </c>
       <c r="K108" s="7">
-        <v>433</v>
+        <v>271</v>
       </c>
       <c r="L108" s="8" t="s">
         <v>15</v>
@@ -5844,7 +5844,7 @@
         <v>47</v>
       </c>
       <c r="K109" s="9">
-        <v>97</v>
+        <v>348</v>
       </c>
       <c r="L109" s="8" t="s">
         <v>15</v>
@@ -5882,7 +5882,7 @@
         <v>38</v>
       </c>
       <c r="K110" s="7">
-        <v>339</v>
+        <v>279</v>
       </c>
       <c r="L110" s="8" t="s">
         <v>15</v>
@@ -5920,7 +5920,7 @@
         <v>42</v>
       </c>
       <c r="K111" s="9">
-        <v>38</v>
+        <v>469</v>
       </c>
       <c r="L111" s="8" t="s">
         <v>15</v>
@@ -5958,7 +5958,7 @@
         <v>47</v>
       </c>
       <c r="K112" s="7">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="L112" s="8" t="s">
         <v>15</v>
@@ -5996,7 +5996,7 @@
         <v>38</v>
       </c>
       <c r="K113" s="9">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="L113" s="8" t="s">
         <v>15</v>
@@ -6034,7 +6034,7 @@
         <v>42</v>
       </c>
       <c r="K114" s="7">
-        <v>197</v>
+        <v>343</v>
       </c>
       <c r="L114" s="8" t="s">
         <v>15</v>
@@ -6072,7 +6072,7 @@
         <v>47</v>
       </c>
       <c r="K115" s="9">
-        <v>375</v>
+        <v>434</v>
       </c>
       <c r="L115" s="8" t="s">
         <v>15</v>
@@ -6110,7 +6110,7 @@
         <v>38</v>
       </c>
       <c r="K116" s="7">
-        <v>452</v>
+        <v>139</v>
       </c>
       <c r="L116" s="8" t="s">
         <v>15</v>
@@ -6148,7 +6148,7 @@
         <v>42</v>
       </c>
       <c r="K117" s="9">
-        <v>34</v>
+        <v>435</v>
       </c>
       <c r="L117" s="8" t="s">
         <v>15</v>
@@ -6186,7 +6186,7 @@
         <v>47</v>
       </c>
       <c r="K118" s="7">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="L118" s="8" t="s">
         <v>15</v>
@@ -6224,7 +6224,7 @@
         <v>38</v>
       </c>
       <c r="K119" s="9">
-        <v>77</v>
+        <v>394</v>
       </c>
       <c r="L119" s="8" t="s">
         <v>15</v>
@@ -6262,7 +6262,7 @@
         <v>42</v>
       </c>
       <c r="K120" s="7">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L120" s="8" t="s">
         <v>15</v>
@@ -6300,7 +6300,7 @@
         <v>47</v>
       </c>
       <c r="K121" s="9">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="L121" s="8" t="s">
         <v>15</v>
@@ -6338,7 +6338,7 @@
         <v>38</v>
       </c>
       <c r="K122" s="7">
-        <v>95</v>
+        <v>415</v>
       </c>
       <c r="L122" s="8" t="s">
         <v>15</v>
@@ -6376,7 +6376,7 @@
         <v>42</v>
       </c>
       <c r="K123" s="9">
-        <v>259</v>
+        <v>207</v>
       </c>
       <c r="L123" s="8" t="s">
         <v>15</v>
@@ -6414,7 +6414,7 @@
         <v>47</v>
       </c>
       <c r="K124" s="7">
-        <v>137</v>
+        <v>378</v>
       </c>
       <c r="L124" s="8" t="s">
         <v>15</v>
@@ -6452,7 +6452,7 @@
         <v>38</v>
       </c>
       <c r="K125" s="9">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="L125" s="8" t="s">
         <v>15</v>
@@ -6490,7 +6490,7 @@
         <v>42</v>
       </c>
       <c r="K126" s="7">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="L126" s="8" t="s">
         <v>15</v>
@@ -6528,7 +6528,7 @@
         <v>47</v>
       </c>
       <c r="K127" s="9">
-        <v>371</v>
+        <v>126</v>
       </c>
       <c r="L127" s="8" t="s">
         <v>15</v>
@@ -6566,7 +6566,7 @@
         <v>38</v>
       </c>
       <c r="K128" s="7">
-        <v>434</v>
+        <v>349</v>
       </c>
       <c r="L128" s="8" t="s">
         <v>15</v>
@@ -6604,7 +6604,7 @@
         <v>42</v>
       </c>
       <c r="K129" s="9">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="L129" s="8" t="s">
         <v>15</v>
@@ -6642,7 +6642,7 @@
         <v>47</v>
       </c>
       <c r="K130" s="7">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="L130" s="8" t="s">
         <v>15</v>
@@ -6680,7 +6680,7 @@
         <v>38</v>
       </c>
       <c r="K131" s="9">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="L131" s="8" t="s">
         <v>15</v>
@@ -6718,7 +6718,7 @@
         <v>42</v>
       </c>
       <c r="K132" s="7">
-        <v>275</v>
+        <v>441</v>
       </c>
       <c r="L132" s="8" t="s">
         <v>15</v>
@@ -6756,7 +6756,7 @@
         <v>47</v>
       </c>
       <c r="K133" s="9">
-        <v>343</v>
+        <v>169</v>
       </c>
       <c r="L133" s="8" t="s">
         <v>15</v>
@@ -6794,7 +6794,7 @@
         <v>38</v>
       </c>
       <c r="K134" s="7">
-        <v>47</v>
+        <v>306</v>
       </c>
       <c r="L134" s="8" t="s">
         <v>15</v>
@@ -6832,7 +6832,7 @@
         <v>42</v>
       </c>
       <c r="K135" s="9">
-        <v>452</v>
+        <v>87</v>
       </c>
       <c r="L135" s="8" t="s">
         <v>15</v>
@@ -6870,7 +6870,7 @@
         <v>47</v>
       </c>
       <c r="K136" s="7">
-        <v>454</v>
+        <v>116</v>
       </c>
       <c r="L136" s="8" t="s">
         <v>15</v>
@@ -6908,7 +6908,7 @@
         <v>38</v>
       </c>
       <c r="K137" s="9">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="L137" s="8" t="s">
         <v>15</v>
@@ -6946,7 +6946,7 @@
         <v>42</v>
       </c>
       <c r="K138" s="7">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="L138" s="10" t="s">
         <v>48</v>
@@ -6984,7 +6984,7 @@
         <v>47</v>
       </c>
       <c r="K139" s="9">
-        <v>58</v>
+        <v>389</v>
       </c>
       <c r="L139" s="8" t="s">
         <v>15</v>
@@ -7022,7 +7022,7 @@
         <v>38</v>
       </c>
       <c r="K140" s="7">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="L140" s="8" t="s">
         <v>15</v>
@@ -7060,7 +7060,7 @@
         <v>42</v>
       </c>
       <c r="K141" s="9">
-        <v>71</v>
+        <v>444</v>
       </c>
       <c r="L141" s="11" t="s">
         <v>102</v>
@@ -7098,7 +7098,7 @@
         <v>47</v>
       </c>
       <c r="K142" s="7">
-        <v>243</v>
+        <v>379</v>
       </c>
       <c r="L142" s="8" t="s">
         <v>15</v>
@@ -7136,7 +7136,7 @@
         <v>38</v>
       </c>
       <c r="K143" s="9">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="L143" s="8" t="s">
         <v>15</v>
@@ -7174,7 +7174,7 @@
         <v>42</v>
       </c>
       <c r="K144" s="7">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="L144" s="8" t="s">
         <v>15</v>
@@ -7212,7 +7212,7 @@
         <v>47</v>
       </c>
       <c r="K145" s="9">
-        <v>297</v>
+        <v>76</v>
       </c>
       <c r="L145" s="8" t="s">
         <v>15</v>
@@ -7250,7 +7250,7 @@
         <v>38</v>
       </c>
       <c r="K146" s="7">
-        <v>408</v>
+        <v>289</v>
       </c>
       <c r="L146" s="8" t="s">
         <v>15</v>
@@ -7288,7 +7288,7 @@
         <v>42</v>
       </c>
       <c r="K147" s="9">
-        <v>110</v>
+        <v>448</v>
       </c>
       <c r="L147" s="8" t="s">
         <v>15</v>
@@ -7326,7 +7326,7 @@
         <v>47</v>
       </c>
       <c r="K148" s="7">
-        <v>407</v>
+        <v>250</v>
       </c>
       <c r="L148" s="8" t="s">
         <v>15</v>
@@ -7364,7 +7364,7 @@
         <v>38</v>
       </c>
       <c r="K149" s="9">
-        <v>99</v>
+        <v>196</v>
       </c>
       <c r="L149" s="8" t="s">
         <v>15</v>
@@ -7402,7 +7402,7 @@
         <v>42</v>
       </c>
       <c r="K150" s="7">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="L150" s="8" t="s">
         <v>15</v>
@@ -7440,7 +7440,7 @@
         <v>47</v>
       </c>
       <c r="K151" s="9">
-        <v>294</v>
+        <v>426</v>
       </c>
       <c r="L151" s="8" t="s">
         <v>15</v>
